--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$64</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2351" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2386" uniqueCount="486">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -437,38 +437,65 @@
     <t>MedicationRequest.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:changeType</t>
+  </si>
+  <si>
+    <t>changeType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/enlist-change}
+</t>
+  </si>
+  <si>
+    <t>EnLiST-Änderungstyp</t>
+  </si>
+  <si>
+    <t>Änderungstyp nach EnLiST — new, modified oder same.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>MedicationRequest.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -620,9 +647,6 @@
   <si>
     <t xml:space="preserve">pattern:$this}
 </t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Directions@@ -1193,6 +1217,9 @@
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1839,7 +1866,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO63"/>
+  <dimension ref="A1:AO64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
@@ -2833,7 +2860,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2852,17 +2879,15 @@
         <v>81</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>139</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>81</v>
@@ -2899,16 +2924,14 @@
         <v>81</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>140</v>
@@ -2932,7 +2955,7 @@
         <v>81</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>81</v>
@@ -2941,48 +2964,46 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>81</v>
       </c>
@@ -3030,7 +3051,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3039,7 +3060,7 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>141</v>
@@ -3051,7 +3072,7 @@
         <v>81</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>81</v>
@@ -3062,14 +3083,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3082,24 +3103,26 @@
         <v>81</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O11" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>81</v>
       </c>
@@ -3147,7 +3170,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3159,30 +3182,30 @@
         <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AO11" t="s" s="2">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>157</v>
-      </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3190,25 +3213,25 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>10</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
         <v>158</v>
@@ -3240,13 +3263,13 @@
         <v>81</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>81</v>
@@ -3264,13 +3287,13 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>81</v>
@@ -3279,27 +3302,27 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AM12" t="s" s="2">
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AN12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" hidden="true">
-      <c r="A13" t="s" s="2">
-        <v>167</v>
-      </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3307,31 +3330,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>10</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3357,13 +3380,13 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
@@ -3381,10 +3404,10 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>90</v>
@@ -3396,27 +3419,27 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
+      <c r="A14" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>177</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3424,31 +3447,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3474,7 +3497,7 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="Y14" t="s" s="2">
         <v>181</v>
@@ -3498,10 +3521,10 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>90</v>
@@ -3522,18 +3545,18 @@
         <v>184</v>
       </c>
       <c r="AN14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AO14" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" hidden="true">
-      <c r="A15" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3544,28 +3567,28 @@
         <v>90</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3591,35 +3614,37 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>193</v>
+        <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>81</v>
@@ -3628,31 +3653,29 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" hidden="true">
+      <c r="A16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AM15" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>196</v>
-      </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>81</v>
       </c>
@@ -3661,7 +3684,7 @@
         <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>91</v>
@@ -3673,16 +3696,16 @@
         <v>81</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3693,46 +3716,44 @@
         <v>81</v>
       </c>
       <c r="S16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="T16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>81</v>
-      </c>
+      <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3750,55 +3771,59 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AM16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" hidden="true">
-      <c r="A17" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="C17" s="2"/>
+      <c r="C17" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="D17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3808,7 +3833,7 @@
         <v>81</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>81</v>
@@ -3823,13 +3848,13 @@
         <v>81</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>81</v>
@@ -3847,13 +3872,13 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>81</v>
@@ -3862,16 +3887,16 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>81</v>
@@ -3879,10 +3904,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3899,23 +3924,21 @@
         <v>81</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>213</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>81</v>
@@ -3940,13 +3963,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>81</v>
+        <v>168</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>81</v>
+        <v>211</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -3964,7 +3987,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3979,7 +4002,7 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>81</v>
@@ -3988,7 +4011,7 @@
         <v>214</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>81</v>
+        <v>215</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
@@ -3996,10 +4019,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4016,21 +4039,23 @@
         <v>81</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4079,7 +4104,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4100,7 +4125,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -4109,12 +4134,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4122,13 +4147,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>81</v>
@@ -4137,17 +4162,15 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -4172,13 +4195,13 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
@@ -4196,10 +4219,10 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>90</v>
@@ -4211,27 +4234,27 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>228</v>
+        <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>230</v>
+        <v>81</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>231</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4254,16 +4277,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4289,13 +4312,13 @@
         <v>81</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>81</v>
+        <v>232</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>81</v>
+        <v>233</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>81</v>
@@ -4313,7 +4336,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>90</v>
@@ -4328,27 +4351,27 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AM21" t="s" s="2">
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AN21" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="22" hidden="true">
-      <c r="A22" t="s" s="2">
-        <v>242</v>
-      </c>
       <c r="B22" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4356,31 +4379,31 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4430,10 +4453,10 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>90</v>
@@ -4445,27 +4468,27 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>250</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4476,7 +4499,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
@@ -4488,15 +4511,17 @@
         <v>81</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M23" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4545,13 +4570,13 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
@@ -4560,27 +4585,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AN23" t="s" s="2">
-        <v>249</v>
-      </c>
       <c r="AO23" t="s" s="2">
-        <v>81</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4591,7 +4616,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>81</v>
@@ -4600,16 +4625,16 @@
         <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4660,13 +4685,13 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>81</v>
@@ -4675,27 +4700,27 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>262</v>
+        <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>263</v>
       </c>
       <c r="AN24" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" hidden="true">
+      <c r="A25" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AO24" t="s" s="2">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>266</v>
-      </c>
       <c r="B25" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4709,7 +4734,7 @@
         <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>81</v>
@@ -4718,13 +4743,13 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4775,7 +4800,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4790,27 +4815,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>271</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>81</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4830,16 +4855,16 @@
         <v>81</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4890,7 +4915,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4905,13 +4930,13 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>278</v>
@@ -4920,7 +4945,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>279</v>
       </c>
@@ -4939,26 +4964,24 @@
         <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>168</v>
+        <v>280</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N27" t="s" s="2">
         <v>282</v>
       </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -4983,13 +5006,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>283</v>
+        <v>81</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>284</v>
+        <v>81</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -5022,16 +5045,16 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
@@ -5039,10 +5062,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5062,18 +5085,20 @@
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>81</v>
@@ -5098,13 +5123,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>81</v>
+        <v>291</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -5122,7 +5147,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5137,16 +5162,16 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>81</v>
+        <v>292</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
@@ -5154,10 +5179,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5168,7 +5193,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>81</v>
@@ -5180,17 +5205,15 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>168</v>
+        <v>295</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -5215,13 +5238,13 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>297</v>
+        <v>81</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>298</v>
+        <v>81</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
@@ -5239,13 +5262,13 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>81</v>
@@ -5254,27 +5277,27 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AO29" t="s" s="2">
-        <v>303</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5297,16 +5320,16 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>305</v>
+        <v>176</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5332,13 +5355,13 @@
         <v>81</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>81</v>
@@ -5356,7 +5379,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5371,19 +5394,19 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5411,7 +5434,7 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>312</v>
@@ -5422,7 +5445,9 @@
       <c r="M31" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N31" s="2"/>
+      <c r="N31" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>81</v>
@@ -5486,16 +5511,16 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>81</v>
+        <v>309</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
@@ -5503,10 +5528,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5529,13 +5554,13 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>104</v>
+        <v>319</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5586,7 +5611,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5601,13 +5626,13 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>81</v>
+        <v>322</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5618,10 +5643,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5644,13 +5669,13 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5701,7 +5726,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5716,13 +5741,13 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -5733,10 +5758,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5747,7 +5772,7 @@
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>81</v>
@@ -5759,18 +5784,16 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>148</v>
+        <v>328</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>329</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
       </c>
@@ -5818,13 +5841,13 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>81</v>
@@ -5833,13 +5856,13 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5850,10 +5873,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5873,21 +5896,21 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N35" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="O35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
       </c>
@@ -5911,13 +5934,13 @@
         <v>81</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>336</v>
+        <v>81</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>337</v>
+        <v>81</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>81</v>
@@ -5935,7 +5958,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5950,7 +5973,7 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>81</v>
+        <v>337</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>81</v>
@@ -5981,7 +6004,7 @@
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -5993,15 +6016,17 @@
         <v>81</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6026,13 +6051,13 @@
         <v>81</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>81</v>
+        <v>343</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>81</v>
+        <v>344</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>81</v>
@@ -6056,7 +6081,7 @@
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
@@ -6065,13 +6090,13 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>343</v>
+        <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6082,10 +6107,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6108,13 +6133,13 @@
         <v>81</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6165,7 +6190,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6180,10 +6205,10 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>350</v>
+        <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>351</v>
@@ -6231,9 +6256,7 @@
       <c r="M38" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="N38" t="s" s="2">
-        <v>356</v>
-      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>81</v>
@@ -6297,10 +6320,10 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>358</v>
@@ -6328,7 +6351,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6348,7 +6371,9 @@
       <c r="M39" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="N39" s="2"/>
+      <c r="N39" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6403,7 +6428,7 @@
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
@@ -6412,13 +6437,13 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>81</v>
+        <v>364</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>363</v>
+        <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
@@ -6429,10 +6454,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6455,13 +6480,13 @@
         <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6512,7 +6537,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6524,16 +6549,16 @@
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>81</v>
+        <v>370</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
@@ -6544,21 +6569,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
@@ -6570,17 +6595,15 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>136</v>
+        <v>373</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>137</v>
+        <v>374</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6629,19 +6652,19 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>81</v>
@@ -6650,7 +6673,7 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6661,14 +6684,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>375</v>
+        <v>149</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6681,26 +6704,24 @@
         <v>81</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -6748,7 +6769,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6769,7 +6790,7 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>133</v>
+        <v>377</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
@@ -6780,44 +6801,46 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>360</v>
+        <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -6865,19 +6888,19 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>81</v>
@@ -6886,7 +6909,7 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>383</v>
+        <v>133</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>81</v>
@@ -6897,10 +6920,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6923,15 +6946,17 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6980,7 +7005,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6992,7 +7017,7 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7001,7 +7026,7 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>81</v>
@@ -7012,21 +7037,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7038,17 +7063,15 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>136</v>
+        <v>373</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>137</v>
+        <v>374</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7097,19 +7120,19 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
@@ -7118,7 +7141,7 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7129,14 +7152,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>375</v>
+        <v>149</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7149,26 +7172,24 @@
         <v>81</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7216,7 +7237,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7237,7 +7258,7 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>133</v>
+        <v>377</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7248,42 +7269,46 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>388</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7331,19 +7356,19 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
@@ -7352,7 +7377,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>391</v>
+        <v>133</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7363,10 +7388,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7389,13 +7414,13 @@
         <v>81</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7446,7 +7471,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7467,7 +7492,7 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7478,10 +7503,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7504,13 +7529,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7561,7 +7586,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7582,7 +7607,7 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7593,10 +7618,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7622,17 +7647,13 @@
         <v>401</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
       </c>
@@ -7680,7 +7701,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7698,10 +7719,10 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>406</v>
+        <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -7749,7 +7770,9 @@
       <c r="N51" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="O51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>81</v>
       </c>
@@ -7815,16 +7838,16 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>415</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -7855,15 +7878,17 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7930,24 +7955,24 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7970,17 +7995,15 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8029,7 +8052,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8047,24 +8070,24 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>81</v>
+        <v>429</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8087,15 +8110,17 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>429</v>
+        <v>401</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -8144,7 +8169,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8162,13 +8187,13 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>81</v>
+        <v>434</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>292</v>
+        <v>81</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>81</v>
@@ -8176,10 +8201,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8202,13 +8227,13 @@
         <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>360</v>
+        <v>437</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8259,7 +8284,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8277,13 +8302,13 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>81</v>
@@ -8291,10 +8316,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8317,13 +8342,13 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>367</v>
+        <v>442</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>368</v>
+        <v>443</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8374,7 +8399,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>369</v>
+        <v>441</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8386,16 +8411,16 @@
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>81</v>
+        <v>444</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>370</v>
+        <v>445</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
@@ -8406,21 +8431,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -8432,17 +8457,15 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>136</v>
+        <v>373</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>137</v>
+        <v>374</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8491,19 +8514,19 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>81</v>
@@ -8512,7 +8535,7 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
@@ -8523,14 +8546,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>375</v>
+        <v>149</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8543,26 +8566,24 @@
         <v>81</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
       </c>
@@ -8610,7 +8631,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8631,7 +8652,7 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>133</v>
+        <v>377</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
@@ -8642,44 +8663,46 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>442</v>
+        <v>135</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>443</v>
+        <v>384</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>444</v>
+        <v>385</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -8703,13 +8726,13 @@
         <v>81</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>447</v>
+        <v>81</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -8727,42 +8750,42 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>441</v>
+        <v>386</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>448</v>
+        <v>133</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>449</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8770,7 +8793,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>90</v>
@@ -8785,7 +8808,7 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>168</v>
+        <v>450</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>451</v>
@@ -8793,7 +8816,9 @@
       <c r="M60" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N60" s="2"/>
+      <c r="N60" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -8818,13 +8843,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -8842,10 +8867,10 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>90</v>
@@ -8860,7 +8885,7 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>456</v>
@@ -8900,13 +8925,13 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8933,13 +8958,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>81</v>
+        <v>461</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>81</v>
+        <v>462</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -8972,38 +8997,38 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>462</v>
+        <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>81</v>
+        <v>465</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>465</v>
+        <v>81</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9015,17 +9040,15 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N62" t="s" s="2">
         <v>469</v>
       </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>81</v>
@@ -9074,13 +9097,13 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
@@ -9089,13 +9112,13 @@
         <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>81</v>
+        <v>470</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>81</v>
+        <v>463</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>81</v>
@@ -9106,14 +9129,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>81</v>
+        <v>473</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9132,16 +9155,16 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9191,7 +9214,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9206,23 +9229,140 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>476</v>
+        <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO63" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO63">
+  <autoFilter ref="A1:AO64">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9232,7 +9372,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI62">
+  <conditionalFormatting sqref="A2:AI63">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-tumorboard-medication-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
